--- a/app/sum-template.xlsx
+++ b/app/sum-template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\yonyou\TidanMgr-R1\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F96E6F-6201-4482-8354-4618A69C709B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD07A5B3-D0F9-41D0-9FF3-5CBF6FA36B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="414" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -40,12 +40,16 @@
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>合计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -96,6 +100,16 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -320,7 +334,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -377,6 +391,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -409,10 +429,10 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
         <top/>
         <bottom/>
       </border>
@@ -441,15 +461,22 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color auto="1"/>
         </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -476,12 +503,13 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color auto="1"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
         <top/>
         <bottom/>
       </border>
@@ -510,12 +538,13 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color auto="1"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
         <top style="thin">
           <color auto="1"/>
         </top>
@@ -552,23 +581,14 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
         <right style="thin">
           <color auto="1"/>
         </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="thin">
-          <color auto="1"/>
-        </vertical>
-        <horizontal/>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -895,9 +915,9 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{22EB78AA-D041-4E6E-AD80-98428E38E537}" name="表3" displayName="表3" ref="B3:D31" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{12412812-B29F-41C0-9907-D58A7306F6A2}" name="序号" totalsRowLabel="汇总" dataDxfId="5" totalsRowDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{B5C9B499-E365-4C50-B304-A51A0E67BFAA}" name="任务名" dataDxfId="4" totalsRowDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{1E4F73FD-77AF-4661-ACBA-522722A3F4E5}" name="数量" totalsRowFunction="count" dataDxfId="3" totalsRowDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{12412812-B29F-41C0-9907-D58A7306F6A2}" name="序号" totalsRowLabel="汇总" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{B5C9B499-E365-4C50-B304-A51A0E67BFAA}" name="任务名" dataDxfId="3" totalsRowDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{1E4F73FD-77AF-4661-ACBA-522722A3F4E5}" name="数量" totalsRowFunction="count" dataDxfId="1" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStylePreset3_Accent1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1159,7 +1179,7 @@
     <col min="1" max="1" width="3.44140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.21875" style="3" customWidth="1"/>
     <col min="3" max="3" width="50.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="3" customWidth="1"/>
     <col min="5" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
@@ -1171,6 +1191,13 @@
     </row>
     <row r="2" spans="1:4" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
+      <c r="C2" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="20">
+        <f>SUM(D4:D200)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:4" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="9" t="s">
